--- a/wl/TEMPALTE.xlsx
+++ b/wl/TEMPALTE.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Desktop\eod_report\wl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99664A71-BE96-4C71-AADB-B73F5EB50038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D7E451-44FA-4DA2-94F0-0852864677C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{7FDFF307-0A6B-4DA0-BF80-593A82D7E9A4}"/>
+    <workbookView xWindow="5280" yWindow="1485" windowWidth="21600" windowHeight="11415" activeTab="5" xr2:uid="{7FDFF307-0A6B-4DA0-BF80-593A82D7E9A4}"/>
   </bookViews>
   <sheets>
     <sheet name="ACTIVE" sheetId="1" r:id="rId1"/>
     <sheet name="PULLED_OUT" sheetId="2" r:id="rId2"/>
-    <sheet name="DNC" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId3"/>
+    <sheet name="DNC" sheetId="3" r:id="rId4"/>
+    <sheet name="S1" sheetId="4" r:id="rId5"/>
+    <sheet name="OVERALL_CYCLE" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="90">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -328,6 +330,21 @@
   </si>
   <si>
     <t>pull out &amp; endorse &amp; update active</t>
+  </si>
+  <si>
+    <t>MATCH FOR NEW ENDO</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>CYCLE</t>
+  </si>
+  <si>
+    <t>POUT LOOKUP</t>
+  </si>
+  <si>
+    <t>DNC(Y/N)</t>
   </si>
 </sst>
 </file>
@@ -397,7 +414,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +463,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA50021"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -460,7 +495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -519,6 +554,15 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1303,42 +1347,40 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"PULLED OUT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
       <formula>"ACTIVE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
       <formula>"CALL"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="CALL&#10;CHECKING">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="CALL&#10;CHECKING">
       <formula>NOT(ISERROR(SEARCH("CALL
 CHECKING",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="DNC&#10;CHECKING">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="DNC&#10;CHECKING">
       <formula>NOT(ISERROR(SEARCH("DNC
 CHECKING",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="FOR PROCESS">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="FOR PROCESS">
       <formula>NOT(ISERROR(SEARCH("FOR PROCESS",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1664,10 +1706,8 @@
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
@@ -1677,6 +1717,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{149FC450-A827-449D-8962-4226322D1D51}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBE20A1-A494-4BD4-8B7B-373F69AC6706}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1733,7 +1782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1536278-830E-466C-A1EB-6A9AA96B27B3}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1791,4 +1840,227 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F32D4-15CC-4696-9137-2C647235239D}">
+  <dimension ref="A1:BA1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="X1" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA1" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB1" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC1" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD1" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE1" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG1" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH1" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI1" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ1" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL1" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN1" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO1" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP1" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ1" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR1" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS1" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT1" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU1" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AV1" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AW1" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX1" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY1" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="BA1" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>